--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Documents\bachelor\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07a1220f59630b3b/Dokumenter/bachelor/bachelor/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E932B9F-AEF9-460D-8315-BC7BC89A649A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{4E932B9F-AEF9-460D-8315-BC7BC89A649A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27644FCB-41E5-4F45-9DBA-6036E881182B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0350460C-A9DD-48DF-A81B-5E589A54FCB0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="2" xr2:uid="{0350460C-A9DD-48DF-A81B-5E589A54FCB0}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="4" r:id="rId1"/>
@@ -463,7 +463,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-tema">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
